--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484842_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484842_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2896</v>
+        <v>0.9263</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2212</v>
+        <v>0.8314</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0684</v>
+        <v>0.0949</v>
       </c>
       <c r="G2" t="n">
         <v>0.4802</v>
@@ -610,13 +610,13 @@
         <v>0.7548</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2433</v>
+        <v>-0.1199</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3556</v>
+        <v>-0.0341</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.699</v>
+        <v>-1.6137</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5163</v>
+        <v>1.5751</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.2153</v>
+        <v>-3.1888</v>
       </c>
       <c r="G3" t="n">
         <v>1.2861</v>
@@ -688,13 +688,13 @@
         <v>2.4531</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.325</v>
+        <v>-1.2398</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6314</v>
+        <v>-0.5726</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6936</v>
+        <v>-0.6672</v>
       </c>
       <c r="V3" t="n">
         <v>-2.7922</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>M. PEREZ MARCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.5305</v>
+        <v>-2.3063</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5639999999999999</v>
+        <v>-1.3063</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.0946</v>
+        <v>-1</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2751</v>
+        <v>-1.8933</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0628</v>
+        <v>-0.1182</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.3379</v>
+        <v>-1.7751</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7716</v>
+        <v>-0.9133</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4212</v>
+        <v>-0.2638</v>
       </c>
       <c r="L4" t="n">
         <v>-0.6496</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0467</v>
+        <v>-0.98</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3584</v>
+        <v>0.1456</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6883</v>
+        <v>-1.1256</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.348</v>
+        <v>-0.3565</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2076</v>
+        <v>-0.393</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5556</v>
+        <v>0.0365</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.113</v>
+        <v>-0.6226</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.113</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PEREZ MARCO</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.6981</v>
+        <v>-2.5948</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6188</v>
+        <v>0.8966</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0794</v>
+        <v>-3.4914</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8933</v>
+        <v>-1.2751</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1182</v>
+        <v>1.0628</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7751</v>
+        <v>-2.3379</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9133</v>
+        <v>0.7716</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2638</v>
+        <v>1.4212</v>
       </c>
       <c r="L5" t="n">
         <v>-0.6496</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.98</v>
+        <v>-2.0467</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1456</v>
+        <v>-0.3584</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1256</v>
+        <v>-1.6883</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7483</v>
+        <v>0.2838</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7055</v>
+        <v>0.125</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0429</v>
+        <v>0.1588</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6226</v>
+        <v>-3.113</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6226</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.1993</v>
+        <v>-3.0935</v>
       </c>
       <c r="E6" t="n">
         <v>-1.8765</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3228</v>
+        <v>-1.217</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1522</v>
@@ -922,13 +922,13 @@
         <v>0.5661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9905</v>
+        <v>-0.8847</v>
       </c>
       <c r="T6" t="n">
         <v>-0.4115</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.579</v>
+        <v>-0.4732</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6226</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ TORRES</t>
+          <t>P. OSAWARU CUENCA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3799</v>
+        <v>-3.0948</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.8932</v>
+        <v>-1.4688</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4867</v>
+        <v>-1.6261</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.6012</v>
+        <v>-4.3563</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3932</v>
+        <v>-1.1958</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.208</v>
+        <v>-3.1605</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.3917</v>
+        <v>-1.7796</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7421</v>
+        <v>-1.1301</v>
       </c>
       <c r="L7" t="n">
         <v>-0.6496</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2095</v>
+        <v>-2.5767</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6511</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5584</v>
+        <v>-2.5109</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5661</v>
+        <v>0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-0.1887</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>0.957</v>
+        <v>0.2048</v>
       </c>
       <c r="T7" t="n">
-        <v>0.442</v>
+        <v>0.1978</v>
       </c>
       <c r="U7" t="n">
-        <v>0.515</v>
+        <v>0.0071</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3018</v>
+        <v>0.3018</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. OSAWARU CUENCA</t>
+          <t>J. DOMINGUEZ TORRES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0351</v>
+        <v>-3.7075</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1709</v>
+        <v>-3.0091</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8642</v>
+        <v>-0.6984</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.3563</v>
+        <v>-4.6012</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1958</v>
+        <v>-2.3932</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.1605</v>
+        <v>-2.208</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7796</v>
+        <v>-2.3917</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1301</v>
+        <v>-1.7421</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6496</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.5767</v>
+        <v>-2.2095</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.6511</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.5109</v>
+        <v>-1.5584</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7548</v>
+        <v>0.5661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7354000000000001</v>
+        <v>0.6294</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5044</v>
+        <v>0.326</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.231</v>
+        <v>0.3034</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3018</v>
+        <v>-0.3018</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6498</v>
+        <v>-4.1954</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6406</v>
+        <v>-1.1333</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.0092</v>
+        <v>-3.0621</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9017</v>
@@ -1156,13 +1156,13 @@
         <v>1.1322</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0499</v>
+        <v>-0.5955</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5632</v>
+        <v>-0.0559</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4867</v>
+        <v>-0.5396</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MUNOZ</t>
+          <t>F. AJAYI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8766</v>
+        <v>-4.5233</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2436</v>
+        <v>-1.531</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.633</v>
+        <v>-2.9923</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7082</v>
+        <v>-3.8573</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9462</v>
+        <v>-1.2295</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7621</v>
+        <v>-2.6278</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4071</v>
+        <v>-0.3492</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5064</v>
+        <v>-1.098</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0993</v>
+        <v>0.7489</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3012</v>
+        <v>-3.5081</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4398</v>
+        <v>-0.1315</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8614</v>
+        <v>-3.3767</v>
       </c>
       <c r="P10" t="n">
+        <v>2.4531</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-0.3774</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.2644</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.887</v>
+        <v>2.8305</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0928</v>
+        <v>-1.8739</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1758</v>
+        <v>-1.1063</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.917</v>
+        <v>-0.7677</v>
       </c>
       <c r="V10" t="n">
+        <v>-1.2452</v>
+      </c>
+      <c r="W10" t="n">
         <v>0.3018</v>
       </c>
-      <c r="W10" t="n">
-        <v>0.6036</v>
-      </c>
       <c r="X10" t="n">
-        <v>-0.3018</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>J. MARTINEZ MUNOZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0377</v>
+        <v>-4.5494</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5456</v>
+        <v>-3.0487</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4922</v>
+        <v>-1.5007</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3973</v>
+        <v>-2.7082</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8188</v>
+        <v>-0.9462</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5785</v>
+        <v>-1.7621</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5403</v>
+        <v>-0.4071</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.1913</v>
+        <v>-0.5064</v>
       </c>
       <c r="L11" t="n">
-        <v>0.651</v>
+        <v>0.0993</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.857</v>
+        <v>-2.3012</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3725</v>
+        <v>-0.4398</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2295</v>
+        <v>-1.8614</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5661</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3209</v>
+        <v>-2.2644</v>
       </c>
       <c r="R11" t="n">
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2462</v>
+        <v>-1.7656</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6554</v>
+        <v>-0.9809</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5909</v>
+        <v>-0.7847</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.4528</v>
+        <v>0.3018</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3398</v>
+        <v>0.6036</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.113</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. AJAYI</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4476</v>
+        <v>-6.3358</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0585</v>
+        <v>-3.4998</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3891</v>
+        <v>-2.8361</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8573</v>
+        <v>-3.3973</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2295</v>
+        <v>-1.8188</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6278</v>
+        <v>-1.5785</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3492</v>
+        <v>-1.5403</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.098</v>
+        <v>-2.1913</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7489</v>
+        <v>0.651</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.5081</v>
+        <v>-1.857</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1315</v>
+        <v>0.3725</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.3767</v>
+        <v>-2.2295</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4531</v>
+        <v>0.5661</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.3774</v>
+        <v>-1.3209</v>
       </c>
       <c r="R12" t="n">
-        <v>2.8305</v>
+        <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.7982</v>
+        <v>-0.0519</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6337</v>
+        <v>-0.2988</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1645</v>
+        <v>0.2469</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2452</v>
+        <v>-3.4528</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3018</v>
+        <v>-0.3398</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.547</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-36.264</v>
+        <v>-35.0882</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.7462</v>
+        <v>-13.5704</v>
       </c>
       <c r="F13" t="n">
-        <v>-21.5181</v>
+        <v>-21.518</v>
       </c>
       <c r="G13" t="n">
         <v>-24.3763</v>
@@ -1459,7 +1459,7 @@
         <v>-18.3981</v>
       </c>
       <c r="P13" t="n">
-        <v>6.604500000000001</v>
+        <v>6.604500000000002</v>
       </c>
       <c r="Q13" t="n">
         <v>-9.435</v>
@@ -1468,10 +1468,10 @@
         <v>16.0395</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.945599999999999</v>
+        <v>-5.7698</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.3801</v>
+        <v>-3.2043</v>
       </c>
       <c r="U13" t="n">
         <v>-2.5655</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>J. SANTONJA FERRERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.1653</v>
+        <v>7.8856</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6574</v>
+        <v>7.0551</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5078</v>
+        <v>0.8305</v>
       </c>
       <c r="G14" t="n">
-        <v>5.432</v>
+        <v>5.3589</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2627</v>
+        <v>0.9344</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1694</v>
+        <v>4.4245</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9506</v>
+        <v>5.5664</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3877</v>
+        <v>1.0988</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5629</v>
+        <v>4.4676</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4814</v>
+        <v>-0.2074</v>
       </c>
       <c r="N14" t="n">
-        <v>0.875</v>
+        <v>-0.1643</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6064000000000001</v>
+        <v>-0.0431</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9435</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1322</v>
+        <v>0.3774</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4879</v>
+        <v>1.2251</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5937</v>
+        <v>0.2627</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8942</v>
+        <v>0.9624</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3018</v>
+        <v>2.8112</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3018</v>
+        <v>3.113</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SANTONJA FERRERO</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.4236</v>
+        <v>7.6914</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2756</v>
+        <v>4.2677</v>
       </c>
       <c r="F15" t="n">
-        <v>1.148</v>
+        <v>3.4238</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3589</v>
+        <v>5.432</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9344</v>
+        <v>3.2627</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4245</v>
+        <v>2.1694</v>
       </c>
       <c r="J15" t="n">
-        <v>5.5664</v>
+        <v>3.9506</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0988</v>
+        <v>2.3877</v>
       </c>
       <c r="L15" t="n">
-        <v>4.4676</v>
+        <v>1.5629</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2074</v>
+        <v>1.4814</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1643</v>
+        <v>0.875</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0431</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5096</v>
+        <v>0.9435</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3774</v>
+        <v>1.1322</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7631</v>
+        <v>1.0141</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5168</v>
+        <v>0.2039</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2798</v>
+        <v>0.8102</v>
       </c>
       <c r="V15" t="n">
-        <v>2.8112</v>
+        <v>0.3018</v>
       </c>
       <c r="W15" t="n">
-        <v>3.113</v>
+        <v>0.3018</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7479</v>
+        <v>6.1604</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5288</v>
+        <v>4.6263</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2191</v>
+        <v>1.5342</v>
       </c>
       <c r="G16" t="n">
         <v>3.4415</v>
@@ -1702,13 +1702,13 @@
         <v>0.7548</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4762</v>
+        <v>0.8887</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0029</v>
+        <v>0.1003</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4733</v>
+        <v>0.7884</v>
       </c>
       <c r="V16" t="n">
         <v>1.2642</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0688</v>
+        <v>4.4957</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4229</v>
+        <v>1.3255</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6459</v>
+        <v>3.1702</v>
       </c>
       <c r="G17" t="n">
         <v>0.4396</v>
@@ -1780,13 +1780,13 @@
         <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.201</v>
+        <v>0.2259</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1205</v>
+        <v>0.023</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3215</v>
+        <v>0.2029</v>
       </c>
       <c r="V17" t="n">
         <v>2.5094</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARRENO</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.535</v>
+        <v>3.7101</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5062</v>
+        <v>2.8054</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0289</v>
+        <v>0.9048</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2183</v>
+        <v>3.5725</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0494</v>
+        <v>0.7325</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8310999999999999</v>
+        <v>2.84</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2872</v>
+        <v>3.2231</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1057</v>
+        <v>1.141</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1816</v>
+        <v>2.0821</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5054999999999999</v>
+        <v>0.3494</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1551</v>
+        <v>-0.4085</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6496</v>
+        <v>0.7579</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7548</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2063</v>
+        <v>0.1377</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4267</v>
+        <v>0.2241</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2204</v>
+        <v>-0.0864</v>
       </c>
       <c r="V18" t="n">
-        <v>2.7922</v>
+        <v>0.9434</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7922</v>
+        <v>1.2452</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>A. VALDERRAMA CARRENO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.345</v>
+        <v>3.6914</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1233</v>
+        <v>3.5062</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2217</v>
+        <v>0.1852</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5725</v>
+        <v>-0.2183</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7325</v>
+        <v>-1.0494</v>
       </c>
       <c r="I19" t="n">
-        <v>2.84</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2231</v>
+        <v>0.2872</v>
       </c>
       <c r="K19" t="n">
-        <v>1.141</v>
+        <v>0.1057</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0821</v>
+        <v>0.1816</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3494</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4085</v>
+        <v>-1.1551</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7579</v>
+        <v>0.6496</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9435</v>
+        <v>0.7548</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9435</v>
+        <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2274</v>
+        <v>0.3627</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.458</v>
+        <v>0.4267</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7695</v>
+        <v>-0.064</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9434</v>
+        <v>2.7922</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2452</v>
+        <v>2.7922</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>R. MAS GANDIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8073</v>
+        <v>1.7762</v>
       </c>
       <c r="E21" t="n">
-        <v>1.8717</v>
+        <v>0.2453</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0644</v>
+        <v>1.5309</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2883</v>
+        <v>2.4606</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8491</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5608</v>
+        <v>1.4722</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5843</v>
+        <v>2.1199</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2794</v>
+        <v>0.0634</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8637</v>
+        <v>2.0565</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8727</v>
+        <v>0.3407</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5697</v>
+        <v>0.925</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.303</v>
+        <v>-0.5843</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1887</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="R21" t="n">
         <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9069</v>
+        <v>0.6365</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6083</v>
+        <v>-0.1007</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2986</v>
+        <v>0.7372</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6226</v>
+        <v>0.3018</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.469</v>
+        <v>1.6495</v>
       </c>
       <c r="E22" t="n">
         <v>0.3173</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1517</v>
+        <v>1.3321</v>
       </c>
       <c r="G22" t="n">
         <v>1.8652</v>
@@ -2170,13 +2170,13 @@
         <v>0.7548</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2075</v>
+        <v>-0.027</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.08989999999999999</v>
+        <v>0.0905</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. MAS GANDIA</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8393</v>
+        <v>0.4277</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2419</v>
+        <v>0.9948</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0812</v>
+        <v>-0.5671</v>
       </c>
       <c r="G24" t="n">
-        <v>2.4606</v>
+        <v>-0.2883</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9883999999999999</v>
+        <v>-0.8491</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4722</v>
+        <v>0.5608</v>
       </c>
       <c r="J24" t="n">
-        <v>2.1199</v>
+        <v>0.5843</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0634</v>
+        <v>-0.2794</v>
       </c>
       <c r="L24" t="n">
-        <v>2.0565</v>
+        <v>0.8637</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3407</v>
+        <v>-0.8727</v>
       </c>
       <c r="N24" t="n">
-        <v>0.925</v>
+        <v>-0.5697</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5843</v>
+        <v>-0.303</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3209</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0757</v>
+        <v>-0.9435</v>
       </c>
       <c r="R24" t="n">
         <v>0.7548</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3004</v>
+        <v>1.5274</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5879</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2875</v>
+        <v>0.796</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.6226</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3018</v>
+        <v>0.6226</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>A. VALDERRAMA CARREÑO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4968</v>
+        <v>0.317</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.9176</v>
+        <v>0.317</v>
       </c>
       <c r="F25" t="n">
-        <v>2.4144</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3.0245</v>
+        <v>0.317</v>
       </c>
       <c r="H25" t="n">
-        <v>3.0506</v>
+        <v>0.317</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0261</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2.8681</v>
+        <v>0.317</v>
       </c>
       <c r="K25" t="n">
-        <v>2.0285</v>
+        <v>0.317</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8396</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1564</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.0221</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8657</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.9627</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.9062</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.435</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1205</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3145</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA CARREÑO</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,58 +2437,58 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.317</v>
+        <v>0.171</v>
       </c>
       <c r="E26" t="n">
-        <v>0.317</v>
+        <v>-1.8202</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.9911</v>
       </c>
       <c r="G26" t="n">
-        <v>0.317</v>
+        <v>3.0245</v>
       </c>
       <c r="H26" t="n">
-        <v>0.317</v>
+        <v>3.0506</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>-0.0261</v>
       </c>
       <c r="J26" t="n">
-        <v>0.317</v>
+        <v>2.8681</v>
       </c>
       <c r="K26" t="n">
-        <v>0.317</v>
+        <v>2.0285</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.8396</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>0.1564</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.0221</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>-0.8657</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-3.9627</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-4.9062</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.1092</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>0.2179</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>0.8913</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.184</v>
+        <v>-3.646</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.4688</v>
+        <v>-5.2482</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2848</v>
+        <v>1.6022</v>
       </c>
       <c r="G27" t="n">
         <v>-4.0732</v>
@@ -2560,13 +2560,13 @@
         <v>0.5661</v>
       </c>
       <c r="S27" t="n">
-        <v>1.6066</v>
+        <v>1.1445</v>
       </c>
       <c r="T27" t="n">
-        <v>1.3731</v>
+        <v>0.5937</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2334</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="V27" t="n">
         <v>1.547</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>36.2642</v>
+        <v>37.56320000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>21.5178</v>
+        <v>21.5181</v>
       </c>
       <c r="F28" t="n">
-        <v>14.7464</v>
+        <v>16.0452</v>
       </c>
       <c r="G28" t="n">
         <v>24.3765</v>
@@ -2638,13 +2638,13 @@
         <v>9.435</v>
       </c>
       <c r="S28" t="n">
-        <v>6.9457</v>
+        <v>8.244800000000001</v>
       </c>
       <c r="T28" t="n">
         <v>2.5654</v>
       </c>
       <c r="U28" t="n">
-        <v>4.38</v>
+        <v>5.679399999999999</v>
       </c>
       <c r="V28" t="n">
         <v>11.5466</v>
